--- a/data/trans_dic/IP31B_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,41; 65,39</t>
+          <t>36,15; 62,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,79; 62,58</t>
+          <t>31,18; 56,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,08; 59,78</t>
+          <t>37,34; 54,81</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,33; 47,56</t>
+          <t>28,53; 37,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,78; 39,8</t>
+          <t>25,7; 33,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,37; 40,19</t>
+          <t>28,02; 34,05</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,05; 35,07</t>
+          <t>23,5; 35,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,08; 36,4</t>
+          <t>21,87; 34,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,12; 34,5</t>
+          <t>24,65; 33,09</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,79; 43,22</t>
+          <t>29,95; 36,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 39,0</t>
+          <t>26,4; 33,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 38,83</t>
+          <t>29,16; 33,93</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>24973</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27725</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52278</t>
+          <t>44493</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16610; 34583</t>
+          <t>18341; 31600</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20887; 34589</t>
+          <t>14099; 25693</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42271; 64650</t>
+          <t>35829; 52591</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>195</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>152790</t>
+          <t>152952</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>176738</t>
+          <t>122696</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329528</t>
+          <t>275648</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>127563; 214142</t>
+          <t>132817; 173498</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>154888; 200259</t>
+          <t>108770; 139823</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>299027; 383166</t>
+          <t>249065; 302677</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42384</t>
+          <t>47933</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54685</t>
+          <t>41587</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97069</t>
+          <t>89520</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33344; 50745</t>
+          <t>39177; 59474</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43620; 65934</t>
+          <t>31839; 49886</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81852; 112398</t>
+          <t>76967; 103320</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>289</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>219727</t>
+          <t>225858</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>192980; 279990</t>
+          <t>204522; 250878</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>233608; 288414</t>
+          <t>162146; 202880</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>442440; 538717</t>
+          <t>378268; 440054</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31B_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>49,22%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>36,15; 62,28</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>31,18; 56,82</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>37,34; 54,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>32,85%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>28,99%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>28,53; 37,27</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>25,7; 33,03</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>28,02; 34,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>28,56%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>23,5; 35,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>21,87; 34,26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24,65; 33,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29,93%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>29,95; 36,73</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26,4; 33,04</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29,16; 33,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4921836339869996</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4317120550794045</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4636886911317359</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>24973</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19520</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44493</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.361477767039981</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3118291087268493</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.3733931234908938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18341; 31600</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14099; 25693</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>35829; 52591</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6227830366615903</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5682337440808863</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5480814501209884</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3285318747444421</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2898759305557378</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3101235433486524</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>152952</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>122696</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>275648</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.2852830138198349</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.256973210354932</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.280215057598901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>132817; 173498</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>108770; 139823</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>249065; 302677</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.3726633499720059</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.330337515572707</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.3405329906071899</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2875656664357394</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.285640184893359</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2866679530201122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>47933</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41587</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>89520</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.2350357756912766</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.2186816419845602</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.2464682639158822</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>39177; 59474</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>31839; 49886</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>76967; 103320</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3568005543211298</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.3426367648369549</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3308582696274202</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.330691749211116</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2993151532710495</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3158369156276572</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>225858</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>183803</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>409662</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.2994523635459768</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.2640466657599407</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.2916332052966374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>204522; 250878</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>162146; 202880</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>378268; 440054</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3673235895481225</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.3303803820841025</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3392681201085116</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>24973</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>19520</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>44493</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>18341</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>14099</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>35829</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>31600</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>25693</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>52591</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>236</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>152952</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>122696</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>275648</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>132817</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>108770</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>249065</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>173498</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>139823</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>302677</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>47933</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>41587</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>89520</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>39177</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>31839</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>76967</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>59474</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>49886</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>103320</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>347</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>225858</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>183803</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>409662</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>204522</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>162146</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>378268</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>250878</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>202880</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>440054</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>